--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:14</t>
+    <t xml:space="preserve">2026-09-09 23:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:09</t>
+    <t xml:space="preserve">2026-09-17 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:05</t>
+    <t xml:space="preserve">2026-09-23 12:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:34</t>
+    <t xml:space="preserve">2026-10-02 13:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:55</t>
+    <t xml:space="preserve">2026-10-04 09:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:00</t>
+    <t xml:space="preserve">2026-10-05 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -643,7 +643,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>328065.12</v>
+        <v>328065.13</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>298943.62</v>
+        <v>298943.63</v>
       </c>
     </row>
     <row r="10">
@@ -1153,7 +1153,7 @@
         <v>2020</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>193251.62</v>
+        <v>193251.63</v>
       </c>
     </row>
     <row r="36">
